--- a/02_Zero_Shot/outputs/Embedding/RoBERTa-base/RESULT_pan_roberta-base_zeroshot.xlsx
+++ b/02_Zero_Shot/outputs/Embedding/RoBERTa-base/RESULT_pan_roberta-base_zeroshot.xlsx
@@ -24159,7 +24159,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.248737279000125</v>
+        <v>14.68902875200001</v>
       </c>
     </row>
     <row r="8">
@@ -24169,7 +24169,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001617796603597212</v>
+        <v>0.01056764658417267</v>
       </c>
     </row>
   </sheetData>
